--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +225 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +329 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.049</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +329 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +225 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.039</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>224 000 € 3 733 €/m² Vente Bar, Brasserie, Tabac 60 m² 60 m² Père Lachaise-Réunion, Paris 20ème arrondissement (75020) Voir l'annonce</t>
+          <t>224 000 € 3 733,33 €/m² Vente Bar, Brasserie, Tabac 60 m² 60 m² Père Lachaise-Réunion, Paris 20ème arrondissement (75020) Voir l'annonce</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +225 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +178 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.049</v>
+        <v>0.0534</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Annonce" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0&quot; €/mois&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +71,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0098351B"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -135,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -149,11 +154,11 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -171,14 +176,17 @@
     <xf numFmtId="168" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -793,7 +801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -929,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +178 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +739 €/mois.</t>
         </is>
       </c>
     </row>
@@ -991,7 +999,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>1750</v>
+        <v>2397</v>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
@@ -1387,7 +1395,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>79/100</t>
+          <t>64/100</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">
@@ -1396,11 +1404,20 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>⚠ AVERTISSEMENT : le rendement affiché par le vendeur est anormalement élevé. Exiger le bail et les quittances avant toute offre — ce dossier reprend le loyer annoncé tel quel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A59:C60"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A13:C14"/>
     <mergeCell ref="A34:C34"/>
@@ -1477,27 +1494,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Année</t>
         </is>
       </c>
-      <c r="B1" s="27" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>Capital dû en début d'année</t>
         </is>
       </c>
-      <c r="C1" s="27" t="inlineStr">
+      <c r="C1" s="28" t="inlineStr">
         <is>
           <t>Intérêts de l'année</t>
         </is>
       </c>
-      <c r="D1" s="27" t="inlineStr">
+      <c r="D1" s="28" t="inlineStr">
         <is>
           <t>Capital remboursé</t>
         </is>
       </c>
-      <c r="E1" s="27" t="inlineStr">
+      <c r="E1" s="28" t="inlineStr">
         <is>
           <t>Capital restant dû</t>
         </is>
@@ -2170,144 +2187,144 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Titre</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Vente Bar, Brasserie, Tabac 60 m²</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Lien</t>
         </is>
       </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>https://www.logic-immo.com/detail-annonce/vente/ile-de-france/paris-75/paris-75000/26J1ZMLZH9SR</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>Ville</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>Paris 20ème arrondissement (75020)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>alerte_logic_immo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Première détection</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Murs libres</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>Caractéristiques</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Évolution du prix</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>stable depuis la première vue</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>Fourchette de marché</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>230 ventes réelles 2023-2025 (DVF)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>Lecture du prix</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Décote sans explication visible dans l'annonce : possible bonne affaire — ou défaut caché (état, copropriété, bail) à vérifier sur place.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Alertes</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>loyer_estime · pepite_sur_loyer_estime</t>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>loyer_estime · rendement_anormalement_eleve</t>
         </is>
       </c>
     </row>
     <row r="12" ht="110" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>224 000 € 3 733,33 €/m² Vente Bar, Brasserie, Tabac 60 m² 60 m² Père Lachaise-Réunion, Paris 20ème arrondissement (75020) Voir l'annonce</t>
         </is>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +739 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +769 €/mois.</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>2397</v>
+        <v>2432.5</v>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
+++ b/docs/dossiers/dossier-paris-20eme-arrondissement-1d739f74.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>loyer_estime · rendement_anormalement_eleve</t>
+          <t>loyer_estime · rendement_anormalement_eleve · occupation_a_confirmer</t>
         </is>
       </c>
     </row>
